--- a/extra/report/No3_課題3テスト結果.xlsx
+++ b/extra/report/No3_課題3テスト結果.xlsx
@@ -3,38 +3,39 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="20417"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{85D55FBE-B4B2-4CB2-8F96-703302983976}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98DCB436-D7DE-4F16-95CB-62911612D74E}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" firstSheet="3" activeTab="19" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="240" yWindow="105" windowWidth="14805" windowHeight="8010" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="ケース1-1" sheetId="2" r:id="rId1"/>
-    <sheet name="ケース1-2" sheetId="3" r:id="rId2"/>
-    <sheet name="ケース2-1" sheetId="4" r:id="rId3"/>
-    <sheet name="ケース2-2" sheetId="5" r:id="rId4"/>
-    <sheet name="ケース3" sheetId="6" r:id="rId5"/>
-    <sheet name="ケース4" sheetId="7" r:id="rId6"/>
-    <sheet name="ケース5-1" sheetId="8" r:id="rId7"/>
-    <sheet name="ケース5-2" sheetId="9" r:id="rId8"/>
-    <sheet name="ケース5-3" sheetId="10" r:id="rId9"/>
-    <sheet name="ケース5-4" sheetId="11" r:id="rId10"/>
-    <sheet name="ケース6-1" sheetId="12" r:id="rId11"/>
-    <sheet name="ケース6-2" sheetId="13" r:id="rId12"/>
-    <sheet name="ケース6-3" sheetId="14" r:id="rId13"/>
-    <sheet name="ケース6-4" sheetId="15" r:id="rId14"/>
-    <sheet name="ケース6-5" sheetId="16" r:id="rId15"/>
-    <sheet name="ケース7-1" sheetId="17" r:id="rId16"/>
-    <sheet name="ケース7-2" sheetId="18" r:id="rId17"/>
-    <sheet name="ケース8" sheetId="19" r:id="rId18"/>
-    <sheet name="ケース9" sheetId="21" r:id="rId19"/>
-    <sheet name="ケース10" sheetId="22" r:id="rId20"/>
+    <sheet name="前提条件" sheetId="23" r:id="rId1"/>
+    <sheet name="ケース1-1" sheetId="2" r:id="rId2"/>
+    <sheet name="ケース1-2" sheetId="3" r:id="rId3"/>
+    <sheet name="ケース2-1" sheetId="4" r:id="rId4"/>
+    <sheet name="ケース2-2" sheetId="5" r:id="rId5"/>
+    <sheet name="ケース3" sheetId="6" r:id="rId6"/>
+    <sheet name="ケース4" sheetId="7" r:id="rId7"/>
+    <sheet name="ケース5-1" sheetId="8" r:id="rId8"/>
+    <sheet name="ケース5-2" sheetId="9" r:id="rId9"/>
+    <sheet name="ケース5-3" sheetId="10" r:id="rId10"/>
+    <sheet name="ケース5-4" sheetId="11" r:id="rId11"/>
+    <sheet name="ケース6-1" sheetId="12" r:id="rId12"/>
+    <sheet name="ケース6-2" sheetId="13" r:id="rId13"/>
+    <sheet name="ケース6-3" sheetId="14" r:id="rId14"/>
+    <sheet name="ケース6-4" sheetId="15" r:id="rId15"/>
+    <sheet name="ケース6-5" sheetId="16" r:id="rId16"/>
+    <sheet name="ケース7-1" sheetId="17" r:id="rId17"/>
+    <sheet name="ケース7-2" sheetId="18" r:id="rId18"/>
+    <sheet name="ケース8" sheetId="19" r:id="rId19"/>
+    <sheet name="ケース9" sheetId="21" r:id="rId20"/>
+    <sheet name="ケース10" sheetId="22" r:id="rId21"/>
   </sheets>
   <calcPr calcId="152511"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="31">
   <si>
     <t>確認内容：サービスメニューに料金情報管理が存在していること。</t>
     <rPh sb="0" eb="4">
@@ -575,6 +576,19 @@
     </rPh>
     <rPh sb="28" eb="30">
       <t>オウカ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>前提条件：データベースに料金情報を登録しておく。</t>
+    <rPh sb="0" eb="4">
+      <t>ゼンテイジョウケン</t>
+    </rPh>
+    <rPh sb="12" eb="16">
+      <t>リョウキンジョウホウ</t>
+    </rPh>
+    <rPh sb="17" eb="19">
+      <t>トウロク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -644,21 +658,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
+      <xdr:row>3</xdr:row>
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>239498</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>48517</xdr:rowOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>87173</xdr:colOff>
+      <xdr:row>27</xdr:row>
+      <xdr:rowOff>67259</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5846CBE6-398E-4C06-AC34-BBED4B7C3CCF}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6CEE7964-4F0B-4747-9CA1-67A56D94940E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -674,6 +688,55 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
+          <a:off x="0" y="514350"/>
+          <a:ext cx="10374173" cy="4182059"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239498</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>48517</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C5B8E1A-6BDC-4B5E-805D-39BD05404C2C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
           <a:off x="0" y="685800"/>
           <a:ext cx="9840698" cy="6392167"/>
         </a:xfrm>
@@ -686,23 +749,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>142875</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>514350</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>28575</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF580689-9860-4626-A3FA-18F570A6640F}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3240409F-E197-49AE-9567-FC610AEAF127}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -710,8 +773,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4257675" y="1476375"/>
-          <a:ext cx="1057275" cy="371475"/>
+          <a:off x="1895475" y="2762250"/>
+          <a:ext cx="7553325" cy="523875"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -753,7 +816,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -868,7 +931,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -983,7 +1046,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1098,7 +1161,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1213,7 +1276,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1328,7 +1391,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1443,7 +1506,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1726,7 +1789,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -1841,7 +1904,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2188,7 +2251,7 @@
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2205,10 +2268,10 @@
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C02A0AD-0868-4847-A120-75266D8084CE}"/>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5846CBE6-398E-4C06-AC34-BBED4B7C3CCF}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2234,69 +2297,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>239498</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>48517</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="4" name="図 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A4609AE-62E7-4B6A-8E08-03A5E7044C98}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="7200900"/>
-          <a:ext cx="9840698" cy="6392167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>552450</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>495300</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>142875</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A54D7E50-18E8-40AD-A496-A9F484B11BA7}"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BF580689-9860-4626-A3FA-18F570A6640F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2304,8 +2323,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1924050" y="2800350"/>
-          <a:ext cx="7486650" cy="447675"/>
+          <a:off x="4257675" y="1476375"/>
+          <a:ext cx="1057275" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2344,25 +2363,118 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239498</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>48517</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{9C02A0AD-0868-4847-A120-75266D8084CE}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9840698" cy="6392167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239498</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>48517</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="4" name="図 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8A4609AE-62E7-4B6A-8E08-03A5E7044C98}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7200900"/>
+          <a:ext cx="9840698" cy="6392167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>66675</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>361950</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>9525</xdr:rowOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>552450</xdr:colOff>
+      <xdr:row>16</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>495300</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="正方形/長方形 5">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE4E174C-EF99-41BC-8B56-BEF8190C63F6}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A54D7E50-18E8-40AD-A496-A9F484B11BA7}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2370,8 +2482,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="428625" y="3324225"/>
-          <a:ext cx="619125" cy="457200"/>
+          <a:off x="1924050" y="2800350"/>
+          <a:ext cx="7486650" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2414,21 +2526,21 @@
     <xdr:from>
       <xdr:col>0</xdr:col>
       <xdr:colOff>428625</xdr:colOff>
-      <xdr:row>58</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
-      <xdr:row>61</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:row>19</xdr:row>
+      <xdr:rowOff>66675</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>361950</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>9525</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EADEA3B5-5962-41C3-A905-5018C9288C57}"/>
+        <xdr:cNvPr id="6" name="正方形/長方形 5">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{CE4E174C-EF99-41BC-8B56-BEF8190C63F6}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2436,8 +2548,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="428625" y="10077450"/>
-          <a:ext cx="9010650" cy="485775"/>
+          <a:off x="428625" y="3324225"/>
+          <a:ext cx="619125" cy="457200"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2478,128 +2590,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>22</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>47625</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CBC5FDE-6336-4172-B309-EF094662EC7F}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr/>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="733425" y="3790950"/>
-          <a:ext cx="0" cy="3409950"/>
-        </a:xfrm>
-        <a:prstGeom prst="straightConnector1">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>239498</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>48517</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F49232B-1A74-4CD1-8CDF-1A8961428B33}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9840698" cy="6392167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>133350</xdr:colOff>
-      <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>504825</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:colOff>428625</xdr:colOff>
+      <xdr:row>58</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>523875</xdr:colOff>
+      <xdr:row>61</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FA78F57-7DF5-4B39-B035-90077E30DF80}"/>
+        <xdr:cNvPr id="7" name="正方形/長方形 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{EADEA3B5-5962-41C3-A905-5018C9288C57}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2607,8 +2614,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4248150" y="1466850"/>
-          <a:ext cx="1057275" cy="371475"/>
+          <a:off x="428625" y="10077450"/>
+          <a:ext cx="9010650" cy="485775"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2647,10 +2654,66 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>22</xdr:row>
+      <xdr:rowOff>19050</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>47625</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="8" name="直線矢印コネクタ 7">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{2CBC5FDE-6336-4172-B309-EF094662EC7F}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr/>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="733425" y="3790950"/>
+          <a:ext cx="0" cy="3409950"/>
+        </a:xfrm>
+        <a:prstGeom prst="straightConnector1">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
-<file path=xl/drawings/drawing20.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/drawings/drawing21.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
@@ -2951,7 +3014,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67D0C3F-5FB5-474E-8556-208E24C87B31}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5F49232B-1A74-4CD1-8CDF-1A8961428B33}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -2982,20 +3045,20 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACB35C84-DD65-4980-B2D0-52182BDC4216}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0FA78F57-7DF5-4B39-B035-90077E30DF80}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3003,7 +3066,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4248150" y="1476375"/>
+          <a:off x="4248150" y="1466850"/>
           <a:ext cx="1057275" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3066,7 +3129,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{211FC652-FECD-45A4-9987-48F1DAEA5D7E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B67D0C3F-5FB5-474E-8556-208E24C87B31}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3110,7 +3173,7 @@
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57AC8361-E342-4CFF-816C-20F2CAAA2A3A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{ACB35C84-DD65-4980-B2D0-52182BDC4216}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3181,7 +3244,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A9B446-4004-456C-96C3-54B2E77DC057}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{211FC652-FECD-45A4-9987-48F1DAEA5D7E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3212,20 +3275,20 @@
       <xdr:col>6</xdr:col>
       <xdr:colOff>133350</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:rowOff>104775</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
       <xdr:colOff>504825</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>123825</xdr:rowOff>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F47BACE2-FB43-491B-B0A5-1F3189E2F895}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{57AC8361-E342-4CFF-816C-20F2CAAA2A3A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3233,7 +3296,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4248150" y="1466850"/>
+          <a:off x="4248150" y="1476375"/>
           <a:ext cx="1057275" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3296,7 +3359,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0426D4A3-3321-4A79-B5D7-759229DBE264}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E9A9B446-4004-456C-96C3-54B2E77DC057}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3322,69 +3385,25 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>42</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>239498</xdr:colOff>
-      <xdr:row>79</xdr:row>
-      <xdr:rowOff>48517</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="3" name="図 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03F59921-3634-438B-9AB8-2A1FCB72CC44}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="7200900"/>
-          <a:ext cx="9840698" cy="6392167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>171450</xdr:colOff>
+      <xdr:colOff>133350</xdr:colOff>
       <xdr:row>8</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>542925</xdr:colOff>
+      <xdr:colOff>504825</xdr:colOff>
       <xdr:row>10</xdr:row>
-      <xdr:rowOff>133350</xdr:rowOff>
+      <xdr:rowOff>123825</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="正方形/長方形 3">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{994BE540-8B99-44F4-878E-77E47A8E87C2}"/>
+        <xdr:cNvPr id="3" name="正方形/長方形 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{F47BACE2-FB43-491B-B0A5-1F3189E2F895}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3392,7 +3411,7 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4286250" y="1476375"/>
+          <a:off x="4248150" y="1466850"/>
           <a:ext cx="1057275" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -3432,25 +3451,118 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239498</xdr:colOff>
+      <xdr:row>41</xdr:row>
+      <xdr:rowOff>48517</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="図 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0426D4A3-3321-4A79-B5D7-759229DBE264}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="685800"/>
+          <a:ext cx="9840698" cy="6392167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>42</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>239498</xdr:colOff>
+      <xdr:row>79</xdr:row>
+      <xdr:rowOff>48517</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="3" name="図 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{03F59921-3634-438B-9AB8-2A1FCB72CC44}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId2"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="0" y="7200900"/>
+          <a:ext cx="9840698" cy="6392167"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>123825</xdr:colOff>
-      <xdr:row>44</xdr:row>
-      <xdr:rowOff>57150</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>390525</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>171450</xdr:colOff>
+      <xdr:row>8</xdr:row>
+      <xdr:rowOff>104775</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>542925</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133350</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="正方形/長方形 4">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6EC34BC-CEA3-4A0D-BA2D-D0867F9176B0}"/>
+        <xdr:cNvPr id="4" name="正方形/長方形 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{994BE540-8B99-44F4-878E-77E47A8E87C2}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3458,8 +3570,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="809625" y="7600950"/>
-          <a:ext cx="2324100" cy="371475"/>
+          <a:off x="4286250" y="1476375"/>
+          <a:ext cx="1057275" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3500,131 +3612,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>600075</xdr:colOff>
-      <xdr:row>10</xdr:row>
-      <xdr:rowOff>133351</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>14288</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>123825</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>57151</xdr:rowOff>
-    </xdr:to>
-    <xdr:cxnSp macro="">
-      <xdr:nvCxnSpPr>
-        <xdr:cNvPr id="7" name="コネクタ: カギ線 6">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEBF5E5E-0412-4908-844B-C638E33DB79B}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvCxnSpPr>
-          <a:stCxn id="4" idx="2"/>
-          <a:endCxn id="5" idx="0"/>
-        </xdr:cNvCxnSpPr>
-      </xdr:nvCxnSpPr>
-      <xdr:spPr>
-        <a:xfrm rot="5400000">
-          <a:off x="516732" y="3302794"/>
-          <a:ext cx="5753100" cy="2843213"/>
-        </a:xfrm>
-        <a:prstGeom prst="bentConnector3">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-          <a:tailEnd type="triangle"/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </xdr:style>
-    </xdr:cxnSp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing7.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-  <xdr:twoCellAnchor editAs="oneCell">
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>0</xdr:colOff>
-      <xdr:row>4</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>239498</xdr:colOff>
-      <xdr:row>41</xdr:row>
-      <xdr:rowOff>48517</xdr:rowOff>
-    </xdr:to>
-    <xdr:pic>
-      <xdr:nvPicPr>
-        <xdr:cNvPr id="2" name="図 1">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B03F20EF-4841-4567-ACF9-AB8328F98F8C}"/>
-            </a:ext>
-          </a:extLst>
-        </xdr:cNvPr>
-        <xdr:cNvPicPr>
-          <a:picLocks noChangeAspect="1"/>
-        </xdr:cNvPicPr>
-      </xdr:nvPicPr>
-      <xdr:blipFill>
-        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1"/>
-        <a:stretch>
-          <a:fillRect/>
-        </a:stretch>
-      </xdr:blipFill>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="0" y="685800"/>
-          <a:ext cx="9840698" cy="6392167"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-      </xdr:spPr>
-    </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>0</xdr:col>
-      <xdr:colOff>400050</xdr:colOff>
-      <xdr:row>12</xdr:row>
       <xdr:rowOff>57150</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>14</xdr:row>
-      <xdr:rowOff>161925</xdr:rowOff>
+      <xdr:col>4</xdr:col>
+      <xdr:colOff>390525</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>85725</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2">
-          <a:extLst>
-            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B48DD32-6F9B-4473-9B97-145977B3045F}"/>
+        <xdr:cNvPr id="5" name="正方形/長方形 4">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C6EC34BC-CEA3-4A0D-BA2D-D0867F9176B0}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3632,8 +3636,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="400050" y="2114550"/>
-          <a:ext cx="1504950" cy="447675"/>
+          <a:off x="809625" y="7600950"/>
+          <a:ext cx="2324100" cy="371475"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3672,6 +3676,65 @@
     </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>600075</xdr:colOff>
+      <xdr:row>10</xdr:row>
+      <xdr:rowOff>133351</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>14288</xdr:colOff>
+      <xdr:row>44</xdr:row>
+      <xdr:rowOff>57151</xdr:rowOff>
+    </xdr:to>
+    <xdr:cxnSp macro="">
+      <xdr:nvCxnSpPr>
+        <xdr:cNvPr id="7" name="コネクタ: カギ線 6">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{BEBF5E5E-0412-4908-844B-C638E33DB79B}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvCxnSpPr>
+          <a:stCxn id="4" idx="2"/>
+          <a:endCxn id="5" idx="0"/>
+        </xdr:cNvCxnSpPr>
+      </xdr:nvCxnSpPr>
+      <xdr:spPr>
+        <a:xfrm rot="5400000">
+          <a:off x="516732" y="3302794"/>
+          <a:ext cx="5753100" cy="2843213"/>
+        </a:xfrm>
+        <a:prstGeom prst="bentConnector3">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:ln w="28575">
+          <a:solidFill>
+            <a:srgbClr val="FF0000"/>
+          </a:solidFill>
+          <a:tailEnd type="triangle"/>
+        </a:ln>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="1">
+          <a:schemeClr val="accent1"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:schemeClr val="accent1"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+    </xdr:cxnSp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -3695,7 +3758,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96F1838A-1AE3-47AF-9E42-9FC4D539452C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{B03F20EF-4841-4567-ACF9-AB8328F98F8C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3724,22 +3787,22 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>0</xdr:col>
-      <xdr:colOff>381000</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>333375</xdr:colOff>
-      <xdr:row>18</xdr:row>
-      <xdr:rowOff>95250</xdr:rowOff>
+      <xdr:colOff>400050</xdr:colOff>
+      <xdr:row>12</xdr:row>
+      <xdr:rowOff>57150</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>533400</xdr:colOff>
+      <xdr:row>14</xdr:row>
+      <xdr:rowOff>161925</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737127BF-F129-4E1A-9C1D-312D719EC516}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7B48DD32-6F9B-4473-9B97-145977B3045F}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3747,8 +3810,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="381000" y="2886075"/>
-          <a:ext cx="638175" cy="295275"/>
+          <a:off x="400050" y="2114550"/>
+          <a:ext cx="1504950" cy="447675"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -3810,7 +3873,7 @@
         <xdr:cNvPr id="2" name="図 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{8C5B8E1A-6BDC-4B5E-805D-39BD05404C2C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{96F1838A-1AE3-47AF-9E42-9FC4D539452C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3838,23 +3901,23 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>523875</xdr:colOff>
+      <xdr:col>0</xdr:col>
+      <xdr:colOff>381000</xdr:colOff>
       <xdr:row>16</xdr:row>
-      <xdr:rowOff>19050</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>19</xdr:row>
-      <xdr:rowOff>28575</xdr:rowOff>
+      <xdr:rowOff>142875</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>333375</xdr:colOff>
+      <xdr:row>18</xdr:row>
+      <xdr:rowOff>95250</xdr:rowOff>
     </xdr:to>
     <xdr:sp macro="" textlink="">
       <xdr:nvSpPr>
         <xdr:cNvPr id="3" name="正方形/長方形 2">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{3240409F-E197-49AE-9567-FC610AEAF127}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{737127BF-F129-4E1A-9C1D-312D719EC516}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -3862,8 +3925,8 @@
       </xdr:nvSpPr>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1895475" y="2762250"/>
-          <a:ext cx="7553325" cy="523875"/>
+          <a:off x="381000" y="2886075"/>
+          <a:ext cx="638175" cy="295275"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -4225,18 +4288,36 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDCD06-741B-4325-A1A8-68455F1E9091}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D928DCB2-C3FE-46E2-BD7E-34A4FC0ED641}">
+  <dimension ref="A2"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>30</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A576D1-1FAB-46D5-BA91-715E4806FDA0}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <sheetData>
     <row r="2" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
-        <v>0</v>
+        <v>12</v>
       </c>
     </row>
   </sheetData>
@@ -4246,7 +4327,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{219698AA-7B31-4EE2-BA05-A5AB24DE2ADB}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4268,7 +4349,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D873E09-EA3A-4233-8EEC-58C60DED2541}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4290,7 +4371,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1D1B4C64-1304-4D43-9560-814FB853543C}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4312,7 +4393,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7EA24341-8EFD-482C-B03F-A282B3009C40}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4334,7 +4415,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{13AE3D19-CB84-467D-9393-83A2EB1B221D}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4356,7 +4437,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{022D3A0E-A045-4A6E-8ACA-760397111540}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4378,7 +4459,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8C2367C-4824-4D99-BEA1-C18E5139A6BC}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4400,7 +4481,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0F71BFE5-3033-4120-B2E9-FBFD95050499}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4422,7 +4503,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5A63077E-95BA-4047-AED7-8E89651DAEBF}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4445,7 +4526,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A4FDCD06-741B-4325-A1A8-68455F1E9091}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>0</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E5D0C8E4-185C-454F-B535-B2511C6A0E36}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4467,7 +4570,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7CC394-11FB-4EBD-8AAE-401A2B69218E}">
+  <dimension ref="A2:A3"/>
+  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
+  <sheetData>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
+      <c r="A3" t="s">
+        <v>27</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{66C33511-EEF7-42B3-8E75-5F08FFC8615A}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4489,29 +4614,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AD7CC394-11FB-4EBD-8AAE-401A2B69218E}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>27</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C8E611FE-E4A2-4986-80BC-A8E1379C2FFD}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4533,7 +4636,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0CC09654-6129-40F4-9DE2-0E4DC56BFACD}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4555,7 +4658,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{271BA5C4-12B9-499C-95FB-E7451B53535B}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4577,7 +4680,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28FF5259-637C-4908-9953-B2DC3C234596}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4599,7 +4702,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F2EB4AE1-5597-44E4-8912-CEC4DEEC3B0B}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4621,7 +4724,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{179006A1-5A1D-44F1-903D-C60DD75B70DE}">
   <dimension ref="A2:A3"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
@@ -4644,41 +4747,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{79A576D1-1FAB-46D5-BA91-715E4806FDA0}">
-  <dimension ref="A2:A3"/>
-  <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <drawing r:id="rId1"/>
-</worksheet>
-</file>
-
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
   <Display>DocumentLibraryForm</Display>
   <Edit>DocumentLibraryForm</Edit>
   <New>DocumentLibraryForm</New>
 </FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
@@ -4840,18 +4921,18 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F8048152-0CA9-47E5-A6CC-6D3980A2E781}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{25A96F8A-B775-40FD-BBE8-4BBDAB58FCAE}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
